--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_1_scientific_construct_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_1_scientific_construct_source_data.xlsx
@@ -738,10 +738,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>569</v>
+        <v>3664</v>
       </c>
       <c r="D2" t="n">
-        <v>569</v>
+        <v>3664</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -754,11 +754,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>wide_interval</t>
+          <t>supported</t>
         </is>
       </c>
     </row>
@@ -772,23 +772,23 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>732</v>
+        <v>15588</v>
       </c>
       <c r="D3" t="n">
-        <v>732</v>
+        <v>3004</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>variable_regime_public</t>
+          <t>variable_public_fallback</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>adequate</t>
+          <t>limited_regime_support</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1106</v>
+        <v>3520</v>
       </c>
       <c r="D4" t="n">
-        <v>1106</v>
+        <v>3520</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>524</v>
+        <v>5400</v>
       </c>
       <c r="D5" t="n">
-        <v>524</v>
+        <v>5400</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -874,23 +874,23 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>465</v>
+        <v>2748</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>2748</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>variable_public_fallback</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>465</v>
+        <v>11691</v>
       </c>
       <c r="D7" t="n">
-        <v>97</v>
+        <v>2253</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -942,10 +942,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>247</v>
+        <v>2640</v>
       </c>
       <c r="D8" t="n">
-        <v>247</v>
+        <v>2640</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -976,23 +976,23 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>465</v>
+        <v>4050</v>
       </c>
       <c r="D9" t="n">
-        <v>98</v>
+        <v>4050</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>variable_public_fallback</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
